--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter2.xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/Chapter2.xlsx
@@ -558,11 +558,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Player_Normal</t>
-        </is>
-      </c>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -602,11 +598,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Angry</t>
-        </is>
-      </c>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -642,11 +634,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Player_Embarrassed</t>
-        </is>
-      </c>
+      <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Player_Embarrassed</t>
@@ -682,11 +670,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Angry</t>
-        </is>
-      </c>
+      <c r="C6" s="2" t="n"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Player_Embarrassed</t>
@@ -722,11 +706,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Player_Angry</t>
-        </is>
-      </c>
+      <c r="C7" s="2" t="n"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Player_Angry</t>
@@ -762,11 +742,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Normal</t>
-        </is>
-      </c>
+      <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Player_Angry</t>
@@ -802,11 +778,7 @@
           <t>Player</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Player_Normal</t>
-        </is>
-      </c>
+      <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
@@ -842,11 +814,7 @@
           <t>Mimi</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Mimi_Angry</t>
-        </is>
-      </c>
+      <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Player_Normal</t>
